--- a/Shiny/Datos limpios/pricing_semanal_historico_soja.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_historico_soja.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M572"/>
+  <dimension ref="A1:M575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -24734,16 +24734,16 @@
         <v>45922</v>
       </c>
       <c r="D567">
-        <v>3943194.35</v>
+        <v>3942409.22</v>
       </c>
       <c r="E567">
-        <v>75248.37</v>
+        <v>75322.2</v>
       </c>
       <c r="F567">
-        <v>39985.77</v>
+        <v>40620.9</v>
       </c>
       <c r="G567">
-        <v>3978456.95</v>
+        <v>3977110.52</v>
       </c>
       <c r="H567">
         <v>640164.45</v>
@@ -24758,7 +24758,7 @@
         <v>638882.0199999999</v>
       </c>
       <c r="L567">
-        <v>4617338.97</v>
+        <v>4615992.54</v>
       </c>
       <c r="M567" t="inlineStr">
         <is>
@@ -24777,16 +24777,16 @@
         <v>45929</v>
       </c>
       <c r="D568">
-        <v>1864499.86</v>
+        <v>1863376.06</v>
       </c>
       <c r="E568">
-        <v>13593.59</v>
+        <v>14566.94</v>
       </c>
       <c r="F568">
         <v>40281.64</v>
       </c>
       <c r="G568">
-        <v>1837811.81</v>
+        <v>1837661.36</v>
       </c>
       <c r="H568">
         <v>461513.12</v>
@@ -24801,7 +24801,7 @@
         <v>460502.49</v>
       </c>
       <c r="L568">
-        <v>2298314.3</v>
+        <v>2298163.85</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
@@ -24820,16 +24820,16 @@
         <v>45936</v>
       </c>
       <c r="D569">
-        <v>927140.8</v>
+        <v>927080.8</v>
       </c>
       <c r="E569">
         <v>14720.14</v>
       </c>
       <c r="F569">
-        <v>25249.67</v>
+        <v>25309.67</v>
       </c>
       <c r="G569">
-        <v>916611.27</v>
+        <v>916491.27</v>
       </c>
       <c r="H569">
         <v>275639.86</v>
@@ -24844,7 +24844,7 @@
         <v>252961.98</v>
       </c>
       <c r="L569">
-        <v>1169573.25</v>
+        <v>1169453.25</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
@@ -24949,33 +24949,162 @@
         <v>45957</v>
       </c>
       <c r="D572">
-        <v>2677.84</v>
+        <v>275694.76</v>
       </c>
       <c r="E572">
+        <v>2521.58</v>
+      </c>
+      <c r="F572">
+        <v>11189.14</v>
+      </c>
+      <c r="G572">
+        <v>267027.2</v>
+      </c>
+      <c r="H572">
+        <v>86572.41</v>
+      </c>
+      <c r="I572">
+        <v>80</v>
+      </c>
+      <c r="J572">
+        <v>30</v>
+      </c>
+      <c r="K572">
+        <v>86622.41</v>
+      </c>
+      <c r="L572">
+        <v>353649.61</v>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573">
+        <v>2025</v>
+      </c>
+      <c r="B573">
+        <v>45</v>
+      </c>
+      <c r="C573" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D573">
+        <v>415929.3</v>
+      </c>
+      <c r="E573">
+        <v>15637.98</v>
+      </c>
+      <c r="F573">
+        <v>8841.51</v>
+      </c>
+      <c r="G573">
+        <v>422725.77</v>
+      </c>
+      <c r="H573">
+        <v>48483.55</v>
+      </c>
+      <c r="I573">
+        <v>2200</v>
+      </c>
+      <c r="J573">
+        <v>132.8</v>
+      </c>
+      <c r="K573">
+        <v>50550.75</v>
+      </c>
+      <c r="L573">
+        <v>473276.52</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574">
+        <v>2025</v>
+      </c>
+      <c r="B574">
+        <v>46</v>
+      </c>
+      <c r="C574" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D574">
+        <v>272004.97</v>
+      </c>
+      <c r="E574">
+        <v>7218.83</v>
+      </c>
+      <c r="F574">
+        <v>7370.28</v>
+      </c>
+      <c r="G574">
+        <v>271853.52</v>
+      </c>
+      <c r="H574">
+        <v>61996.76</v>
+      </c>
+      <c r="I574">
         <v>0</v>
       </c>
-      <c r="F572">
+      <c r="J574">
+        <v>311.65</v>
+      </c>
+      <c r="K574">
+        <v>61685.11</v>
+      </c>
+      <c r="L574">
+        <v>333538.6299999999</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>SOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575">
+        <v>2025</v>
+      </c>
+      <c r="B575">
+        <v>47</v>
+      </c>
+      <c r="C575" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D575">
+        <v>259822.1</v>
+      </c>
+      <c r="E575">
+        <v>2967.96</v>
+      </c>
+      <c r="F575">
+        <v>400.52</v>
+      </c>
+      <c r="G575">
+        <v>262389.54</v>
+      </c>
+      <c r="H575">
+        <v>89459.39999999999</v>
+      </c>
+      <c r="I575">
         <v>0</v>
       </c>
-      <c r="G572">
-        <v>2677.84</v>
-      </c>
-      <c r="H572">
-        <v>0</v>
-      </c>
-      <c r="I572">
-        <v>0</v>
-      </c>
-      <c r="J572">
-        <v>0</v>
-      </c>
-      <c r="K572">
-        <v>0</v>
-      </c>
-      <c r="L572">
-        <v>2677.84</v>
-      </c>
-      <c r="M572" t="inlineStr">
+      <c r="J575">
+        <v>420</v>
+      </c>
+      <c r="K575">
+        <v>89039.39999999999</v>
+      </c>
+      <c r="L575">
+        <v>351428.9399999999</v>
+      </c>
+      <c r="M575" t="inlineStr">
         <is>
           <t>SOJA</t>
         </is>
